--- a/Sim/Scenario_H2_Figures/tables_output_summary_2050.xlsx
+++ b/Sim/Scenario_H2_Figures/tables_output_summary_2050.xlsx
@@ -424,16 +424,16 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="C2">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="D2">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="E2">
-        <v>2.6</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -441,16 +441,16 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="C3">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="D3">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="E3">
-        <v>1.94</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -464,10 +464,10 @@
         <v>0.59</v>
       </c>
       <c r="D4">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="E4">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -475,16 +475,16 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="C5">
-        <v>2.55</v>
+        <v>2.44</v>
       </c>
       <c r="D5">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="E5">
-        <v>3.06</v>
+        <v>3.22</v>
       </c>
     </row>
   </sheetData>
@@ -536,16 +536,16 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="C3">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -579,7 +579,7 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
